--- a/02_Inputs/SEA Quizzes.xlsx
+++ b/02_Inputs/SEA Quizzes.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/SEH/Sustainable Energy Academy/CMS/02_Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Quizzes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B289D4B3-F6D4-9E44-B743-F5D6838B8588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{070FAC4B-D145-4859-B9E3-DA8B24BBCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="740" windowWidth="27200" windowHeight="11480" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="21800" windowHeight="12980" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Module 1" sheetId="3" r:id="rId2"/>
     <sheet name="Module 2" sheetId="4" r:id="rId3"/>
-    <sheet name="Module 4" sheetId="5" r:id="rId4"/>
-    <sheet name="Module 8" sheetId="2" r:id="rId5"/>
+    <sheet name="Module 3" sheetId="6" r:id="rId4"/>
+    <sheet name="Module 4" sheetId="5" r:id="rId5"/>
+    <sheet name="Module 5" sheetId="8" r:id="rId6"/>
+    <sheet name="Module 6" sheetId="9" r:id="rId7"/>
+    <sheet name="Module 7" sheetId="7" r:id="rId8"/>
+    <sheet name="Module 8" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="389">
   <si>
     <t>Question Text</t>
   </si>
@@ -168,7 +172,7 @@
     <t xml:space="preserve">Hydropower plays a dominant role in the Arab States. While 7% of power flows from renewable sources, about 3.4% comes specifically from hydropower. It has the largest installed capacity at 11.2 GW. </t>
   </si>
   <si>
-    <t>In which region would off-grid and decentralized power be particularly helpful?</t>
+    <t>Which region has the largest energy access gap?</t>
   </si>
   <si>
     <t>Asia-Pacific</t>
@@ -255,7 +259,7 @@
     <t>Green hydrogen can be produced using abundant low-cost solar and wind resources in these countries and then exported as a clean fuel</t>
   </si>
   <si>
-    <t>1. What is the main goal of SDG 7?</t>
+    <t>What is the main goal of SDG 7?</t>
   </si>
   <si>
     <t>Ensure universal access to clean water and sanitation</t>
@@ -273,7 +277,7 @@
     <t>SDG 7 specifically aims to ensure access to affordable, reliable, sustainable and modern energy for all.</t>
   </si>
   <si>
-    <t>2. Which of the following are components of sustainable energy access? (Select all that apply)</t>
+    <t>Which of the following are components of sustainable energy access? (Select all that apply)</t>
   </si>
   <si>
     <t>Availability</t>
@@ -285,10 +289,13 @@
     <t>Adequacy</t>
   </si>
   <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
     <t>Sustainable energy access includes availability, affordability, adequacy, safety, reliability, and low-carbon compatibility.</t>
   </si>
   <si>
-    <t>3. Approximately how many people globally still lack access to electricity?</t>
+    <t>Approximately how many people globally still lack access to electricity?</t>
   </si>
   <si>
     <t>500 million</t>
@@ -306,10 +313,10 @@
     <t>According to the 2024 SDG 7 Tracking Report, around 685 million people lack electricity access.</t>
   </si>
   <si>
-    <t>4. What is the difference between energy access and inclusive energy services?</t>
-  </si>
-  <si>
-    <t>Energy access is about quantity; inclusive services consider quality and equity</t>
+    <t>What is the difference between energy access and inclusive energy services?</t>
+  </si>
+  <si>
+    <t>ADEF</t>
   </si>
   <si>
     <t>Inclusive energy services are more expensive</t>
@@ -321,7 +328,7 @@
     <t>Energy access refers to having energy, while inclusive services consider equity, quality, and usability for all.</t>
   </si>
   <si>
-    <t>5. Which human rights are most directly impacted by energy access? (Select all that apply)</t>
+    <t>Which human rights are most directly impacted by energy access? (Select all that apply)</t>
   </si>
   <si>
     <t>Right to education</t>
@@ -339,7 +346,7 @@
     <t>Energy access is critical to the right to education, health, and an adequate standard of living. The right to bear arms is not internationally recognized as a human right.</t>
   </si>
   <si>
-    <t>6. What is considered a clean cooking solution?</t>
+    <t>What is considered a clean cooking solution?</t>
   </si>
   <si>
     <t>Charcoal in open fires</t>
@@ -354,7 +361,7 @@
     <t>Electric induction stoves are clean cooking solutions, unlike charcoal or kerosene which contribute to indoor air pollution.</t>
   </si>
   <si>
-    <t>7. Which of the following is NOT part of the Multi-Tier Framework (MTF) for measuring energy access?</t>
+    <t>Which of the following is NOT part of the Multi-Tier Framework (MTF) for measuring energy access?</t>
   </si>
   <si>
     <t>Quality of energy service</t>
@@ -369,7 +376,7 @@
     <t>MTF includes quality, reliability, and affordability but not energy efficiency rating as a core indicator.</t>
   </si>
   <si>
-    <t>8. What proportion of global clean cooking access deficit is concentrated in Sub-Saharan Africa?</t>
+    <t>What proportion of global clean cooking access deficit is concentrated in Sub-Saharan Africa?</t>
   </si>
   <si>
     <t>Over 80%</t>
@@ -393,6 +400,9 @@
     <t>Industrial sewing machines</t>
   </si>
   <si>
+    <t>1,3,4</t>
+  </si>
+  <si>
     <t>Productive uses of energy are those that generate income or improve economic output, like irrigation, cold storage, and industrial appliances.</t>
   </si>
   <si>
@@ -414,6 +424,186 @@
     <t>Energy Access Explorer uses geospatial data to identify areas for energy intervention planning.</t>
   </si>
   <si>
+    <t>What is a key origin of the concept of a just energy transition?</t>
+  </si>
+  <si>
+    <t>A UN intergovernmental panel on emissions</t>
+  </si>
+  <si>
+    <t>A youth climate advocacy network</t>
+  </si>
+  <si>
+    <t>Trade unions advocating for worker protections</t>
+  </si>
+  <si>
+    <t>A corporate sustainability campaign</t>
+  </si>
+  <si>
+    <t>The term originated in trade union movements, emphasizing worker protections during environmental reforms.</t>
+  </si>
+  <si>
+    <t>Which principle is central to achieving a just transition across diverse contexts?</t>
+  </si>
+  <si>
+    <t>Standardizing transition timelines</t>
+  </si>
+  <si>
+    <t>Universal subsidy models</t>
+  </si>
+  <si>
+    <t>Tailoring strategies to local realities</t>
+  </si>
+  <si>
+    <t>Avoiding community consultation</t>
+  </si>
+  <si>
+    <t>Tailored strategies are crucial to account for regional disparities, social dynamics, and economic contexts.</t>
+  </si>
+  <si>
+    <t>What does “energy justice” emphasize most clearly?</t>
+  </si>
+  <si>
+    <t>Maximizing grid efficiency</t>
+  </si>
+  <si>
+    <t>Equal distribution of energy benefits and burdens</t>
+  </si>
+  <si>
+    <t>Prioritizing large-scale infrastructure</t>
+  </si>
+  <si>
+    <t>Deregulation of energy markets</t>
+  </si>
+  <si>
+    <t>Energy justice focuses on equitable access, fair distribution, and inclusion in energy decisions.</t>
+  </si>
+  <si>
+    <t>Which of the following best describes a procedural justice approach in energy planning?</t>
+  </si>
+  <si>
+    <t>Evaluating only technical feasibility</t>
+  </si>
+  <si>
+    <t>Centralizing decision-making in ministries</t>
+  </si>
+  <si>
+    <t>Prioritizing speed over consultation</t>
+  </si>
+  <si>
+    <t>Including stakeholders in all phases of project design</t>
+  </si>
+  <si>
+    <t>Procedural justice requires inclusive, transparent participation in all phases of energy planning.</t>
+  </si>
+  <si>
+    <t>What challenge may arise from a poorly planned shift away from fossil fuels in extractive-dependent regions?</t>
+  </si>
+  <si>
+    <t>More foreign investment</t>
+  </si>
+  <si>
+    <t>Reduction in electricity prices</t>
+  </si>
+  <si>
+    <t>Job losses and social instability</t>
+  </si>
+  <si>
+    <t>Faster energy access</t>
+  </si>
+  <si>
+    <t>Rapid transitions without economic alternatives can destabilize communities dependent on extractive industries.</t>
+  </si>
+  <si>
+    <t>What is a key gender-related barrier to equitable participation in the energy transition?</t>
+  </si>
+  <si>
+    <t>Lack of interest among women in energy jobs</t>
+  </si>
+  <si>
+    <t>Women's preference for informal energy solutions</t>
+  </si>
+  <si>
+    <t>Underrepresentation in leadership and unequal access to training and financing</t>
+  </si>
+  <si>
+    <t>Resistance from male-dominated unions</t>
+  </si>
+  <si>
+    <t>Structural barriers—such as limited access to training, financing, and leadership roles—limit women's full participation in the energy sector.</t>
+  </si>
+  <si>
+    <t>Why is land tenure security essential in renewable energy deployment in the Global South?</t>
+  </si>
+  <si>
+    <t>It ensures lower electricity prices for communities</t>
+  </si>
+  <si>
+    <t>It guarantees investors higher returns</t>
+  </si>
+  <si>
+    <t>It prevents displacement, protects community rights, and ensures equitable benefit sharing</t>
+  </si>
+  <si>
+    <t>It allows governments to bypass consultation requirements</t>
+  </si>
+  <si>
+    <t>Secure land rights help prevent displacement, protect livelihoods, and facilitate fair participation in renewable energy benefits.</t>
+  </si>
+  <si>
+    <t>What is a major environmental concern linked to large-scale hydropower projects?</t>
+  </si>
+  <si>
+    <t>High emissions from turbines</t>
+  </si>
+  <si>
+    <t>Energy loss in long-distance transmission</t>
+  </si>
+  <si>
+    <t>Disruption of aquatic ecosystems and methane emissions from reservoirs</t>
+  </si>
+  <si>
+    <t>Overdependence on imported technology</t>
+  </si>
+  <si>
+    <t>Large-scale hydropower can disrupt river ecosystems and emit methane from decomposing biomass in reservoirs, especially in tropical zones.</t>
+  </si>
+  <si>
+    <t>Which strategy promotes equitable economic opportunities in energy transitions?</t>
+  </si>
+  <si>
+    <t>Tax breaks for utilities</t>
+  </si>
+  <si>
+    <t>Skills development and retraining programs</t>
+  </si>
+  <si>
+    <t>Privatizing energy access</t>
+  </si>
+  <si>
+    <t>Relying on carbon markets alone</t>
+  </si>
+  <si>
+    <t>Skills development and retraining enable workers and communities to benefit from new energy sectors.</t>
+  </si>
+  <si>
+    <t>What is the role of Free, Prior and Informed Consent (FPIC) in just transitions?</t>
+  </si>
+  <si>
+    <t>To speed up infrastructure development</t>
+  </si>
+  <si>
+    <t>To bypass government approvals</t>
+  </si>
+  <si>
+    <t>To ensure indigenous communities have decision-making power over energy projects</t>
+  </si>
+  <si>
+    <t>To limit access to natural resources</t>
+  </si>
+  <si>
+    <t>FPIC ensures that Indigenous peoples are meaningfully involved in decisions affecting their lands and lives.</t>
+  </si>
+  <si>
     <t>What are the three key factors ESG stands for in sustainable energy finance?</t>
   </si>
   <si>
@@ -447,6 +637,9 @@
     <t>Risk management</t>
   </si>
   <si>
+    <t>1,2,4</t>
+  </si>
+  <si>
     <t>Sustainable finance enhances corporate responsibility, creates long-term value, and manages risk by integrating ESG factors into decision-making.</t>
   </si>
   <si>
@@ -594,6 +787,369 @@
     <t>Supportive instruments include feed-in tariffs, carbon pricing, and energy performance contracts. Fuel subsidies generally discourage renewables.</t>
   </si>
   <si>
+    <t>What percentage of total global greenhouse gas emissions is attributed to the energy sector?</t>
+  </si>
+  <si>
+    <t>About 45%</t>
+  </si>
+  <si>
+    <t>Around 60%</t>
+  </si>
+  <si>
+    <t>Approximately 75%</t>
+  </si>
+  <si>
+    <t>Less than 25%</t>
+  </si>
+  <si>
+    <t>The energy sector is responsible for roughly 75% of total global GHG emissions, making it the largest contributor to climate change.</t>
+  </si>
+  <si>
+    <t>Which of the following greenhouse gases has the highest global warming potential (GWP) among those commonly emitted by the energy sector?</t>
+  </si>
+  <si>
+    <t>Carbon dioxide (CO₂)</t>
+  </si>
+  <si>
+    <t>Methane (CH₄)</t>
+  </si>
+  <si>
+    <t>Nitrous oxide (N₂O)</t>
+  </si>
+  <si>
+    <t>Sulfur hexafluoride (SF₆)</t>
+  </si>
+  <si>
+    <t>SF₆ has the highest GWP—about 25,200 times that of CO₂—making it a critical target for emission reductions in energy distribution.</t>
+  </si>
+  <si>
+    <t>What are key environmental impacts associated with the development of renewable energy infrastructure?</t>
+  </si>
+  <si>
+    <t>Habitat disruption</t>
+  </si>
+  <si>
+    <t>Air pollution from power plants</t>
+  </si>
+  <si>
+    <t>Land use conflicts</t>
+  </si>
+  <si>
+    <t>Mineral extraction impacts</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4</t>
+  </si>
+  <si>
+    <t>All options are correct. Habitat disruption and land use conflicts arise from large-scale installations, air pollution can occur during material production and decommissioning, and mining for minerals needed in solar panels, wind turbines, and batteries causes serious environmental degradation.</t>
+  </si>
+  <si>
+    <t>How does climate change impact the performance and reliability of energy systems?</t>
+  </si>
+  <si>
+    <t>It increases cooling demand during heatwaves, stressing electricity grids</t>
+  </si>
+  <si>
+    <t>It improves thermal plant efficiency by warming water sources</t>
+  </si>
+  <si>
+    <t>It disrupts hydropower generation due to changing rainfall patterns</t>
+  </si>
+  <si>
+    <t>It increases the risk of infrastructure failure from extreme weather events</t>
+  </si>
+  <si>
+    <t>1, 3, 4</t>
+  </si>
+  <si>
+    <t>Climate change stresses systems by increasing cooling needs, disrupting hydropower, and exposing infrastructure to weather extremes. Warmer water actually reduces—not improves—thermal plant efficiency.</t>
+  </si>
+  <si>
+    <t>What are key challenges limiting the widespread adoption of renewable energy technologies in developing countries?</t>
+  </si>
+  <si>
+    <t>High initial capital costs and financing constraints</t>
+  </si>
+  <si>
+    <t>Lack of technical capacity and skilled labor</t>
+  </si>
+  <si>
+    <t>Volatile markets and infrastructure limitations</t>
+  </si>
+  <si>
+    <t>Inconsistent policies and weak grid integration</t>
+  </si>
+  <si>
+    <t>All listed options are documented constraints: high costs, skills gaps, market volatility, and policy/infrastructure weaknesses.</t>
+  </si>
+  <si>
+    <t>Which of the following accurately describe lifecycle emissions from energy technologies?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifecycle emissions account for all stages from resource extraction to decommissioning </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solar and wind have significantly lower lifecycle emissions than coal or gas </t>
+  </si>
+  <si>
+    <t>Natural gas and coal are comparable to wind and solar in lifecycle emissions</t>
+  </si>
+  <si>
+    <t>Lifecycle emissions are only relevant for fossil fuels</t>
+  </si>
+  <si>
+    <t>Lifecycle analysis provides a comprehensive view of emissions. Wind (13g CO₂/kWh) and solar (43g CO₂/kWh) are far lower than coal (1,001g) and natural gas (486g). Lifecycle analysis is relevant for all energy types.</t>
+  </si>
+  <si>
+    <t>Which sector is the largest contributor to global CO2 emissions from end-use sectors?</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Transport is the largest source of end-use CO2 emissions, responsible for over one-third, making it a priority sector for decarbonization through electrification and efficiency improvements.</t>
+  </si>
+  <si>
+    <t>A Ministry of Energy seeks to optimize off-grid investments in underserved rural zones but has limited household-level data. Which of the following techniques could most effectively identify priority areas for electrification?</t>
+  </si>
+  <si>
+    <t>Cost–Benefit Analysis using national grid maps</t>
+  </si>
+  <si>
+    <t>Supervised Machine Learning using labeled access data and satellite imagery</t>
+  </si>
+  <si>
+    <t>Surveys with national census teams</t>
+  </si>
+  <si>
+    <t>Public consultation reports</t>
+  </si>
+  <si>
+    <t>Supervised ML trained on remote sensing and labeled access data can estimate electrification status and prioritize interventions.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Which of the following is a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>necessary condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for using energy data to support gender-transformative policy design?</t>
+    </r>
+  </si>
+  <si>
+    <t>Aggregated national energy supply figures</t>
+  </si>
+  <si>
+    <t>Smart meter deployment in capital cities</t>
+  </si>
+  <si>
+    <t>Disaggregated data across gender, income, and location</t>
+  </si>
+  <si>
+    <t>Technical capacity in the private sector</t>
+  </si>
+  <si>
+    <t>Only disaggregated data can reveal energy access inequalities and support targeted, gender-responsive policies.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You are supporting a PM&amp;E strategy for a regional clean cooking program. Which of the following indicators would provide </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>actionable insights</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> into intersectional equity?</t>
+    </r>
+  </si>
+  <si>
+    <t>LPG consumption in rural vs urban areas</t>
+  </si>
+  <si>
+    <t>Stove emissions data only</t>
+  </si>
+  <si>
+    <t>Average fuel cost per kilogram</t>
+  </si>
+  <si>
+    <t>Time poverty burden for women in woodfuel-dependent households</t>
+  </si>
+  <si>
+    <t>Time poverty reveals structural burdens faced by women and is critical for intersectional energy planning.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Which principle of the UN Fundamental Principles of Official Statistics is </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>most directly threatened</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when private smart meter data is used without clear consent or anonymization?</t>
+    </r>
+  </si>
+  <si>
+    <t>Principle 2: Professional and ethical methods</t>
+  </si>
+  <si>
+    <t>Principle 4: Right to comment on misinterpretation</t>
+  </si>
+  <si>
+    <t>Principle 7: Transparency of laws</t>
+  </si>
+  <si>
+    <t>Principle 10: International cooperation</t>
+  </si>
+  <si>
+    <t>Using personal data without safeguards breaches professional ethics and undermines trust.</t>
+  </si>
+  <si>
+    <t>A government wants to use machine learning to target electricity subsidies. What is a key ethical risk if training data is drawn only from urban consumers?</t>
+  </si>
+  <si>
+    <t>Overfitting the model to low-income contexts</t>
+  </si>
+  <si>
+    <t>Over-subsidizing rural areas</t>
+  </si>
+  <si>
+    <t>Algorithmic bias reinforcing exclusion of rural and informal households</t>
+  </si>
+  <si>
+    <t>Model instability due to grid reliability</t>
+  </si>
+  <si>
+    <t>Biased training data can systematically exclude underserved groups, reinforcing inequality.</t>
+  </si>
+  <si>
+    <t>What is a key advantage of using prescriptive analytics over predictive analytics in energy transition planning?</t>
+  </si>
+  <si>
+    <t>It forecasts climate scenarios</t>
+  </si>
+  <si>
+    <t>It allocates capital expenditure in national budgets</t>
+  </si>
+  <si>
+    <t>It recommends specific actions based on predicted outcomes</t>
+  </si>
+  <si>
+    <t>It replaces stakeholder engagement</t>
+  </si>
+  <si>
+    <t>Prescriptive models translate predictions into concrete decision pathways for planners.</t>
+  </si>
+  <si>
+    <t>In contexts where real-time monitoring is essential (e.g. for distributed solar networks), what architecture is most effective to reduce latency and dependence on central servers?</t>
+  </si>
+  <si>
+    <t>Cloud-only computing with weekly updates</t>
+  </si>
+  <si>
+    <t>Manual logbooks updated monthly</t>
+  </si>
+  <si>
+    <t>Edge computing for localized decision-making</t>
+  </si>
+  <si>
+    <t>Social audits using community dashboards</t>
+  </si>
+  <si>
+    <t>Edge computing allows real-time, local processing critical for adaptive energy systems.</t>
+  </si>
+  <si>
+    <t>A country has just adopted OSeMOSYS for long-term planning. What is its main value for policymakers?</t>
+  </si>
+  <si>
+    <t>It visualizes renewable logos for public campaigns</t>
+  </si>
+  <si>
+    <t>It automates tariff reforms</t>
+  </si>
+  <si>
+    <t>It enables simulation of different energy policy scenarios and investment pathways</t>
+  </si>
+  <si>
+    <t>It substitutes for national accounts</t>
+  </si>
+  <si>
+    <t>OSeMOSYS models techno-economic pathways under constraints and helps test policy impacts.</t>
+  </si>
+  <si>
+    <t>In institutionalizing data governance, what is the main value of establishing a regulatory sandbox in the energy sector?</t>
+  </si>
+  <si>
+    <t>It lowers energy prices immediately</t>
+  </si>
+  <si>
+    <t>It delays regulation for startups</t>
+  </si>
+  <si>
+    <t>It provides a safe space to test data-driven innovation under monitored conditions</t>
+  </si>
+  <si>
+    <t>It bypasses public procurement rules</t>
+  </si>
+  <si>
+    <t>Sandboxes let regulators and innovators co-design and test new energy data solutions before full implementation.</t>
+  </si>
+  <si>
     <t>What is one of the main factors driving increased electricity demand in buildings by 2050?</t>
   </si>
   <si>
@@ -742,22 +1298,13 @@
   </si>
   <si>
     <t>According to IPCC-aligned pathways, nearly all new capacity additions by 2050 are expected to be from renewables.</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>1,3,4</t>
-  </si>
-  <si>
-    <t>1,2,4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,16 +1362,75 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -832,11 +1438,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -850,6 +1471,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -871,6 +1495,32 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,15 +1870,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.5" customWidth="1"/>
-    <col min="2" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.95">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="45" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,15 +1924,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:7" ht="45" customHeight="1"/>
+    <row r="4" spans="1:7" ht="45" customHeight="1"/>
+    <row r="5" spans="1:7" ht="45" customHeight="1"/>
+    <row r="6" spans="1:7" ht="45" customHeight="1"/>
+    <row r="7" spans="1:7" ht="45" customHeight="1"/>
+    <row r="8" spans="1:7" ht="45" customHeight="1"/>
+    <row r="9" spans="1:7" ht="45" customHeight="1"/>
+    <row r="10" spans="1:7" ht="45" customHeight="1"/>
+    <row r="11" spans="1:7" ht="45" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1291,16 +1941,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4593A5-F2BF-4881-B433-81FC04EC7350}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.5" style="11" customWidth="1"/>
-    <col min="2" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" style="12" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="15" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="17.100000000000001">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1315,41 +1965,41 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="14" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B2" s="17">
         <v>0.75</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="17">
         <v>0.9</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>0.6</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="17">
         <v>0.3</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:7" ht="45" customHeight="1">
+      <c r="A3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
@@ -1361,14 +2011,14 @@
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <v>3</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="45" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>22</v>
       </c>
@@ -1384,37 +2034,37 @@
       <c r="E4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="18">
         <v>4</v>
       </c>
       <c r="G4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="14" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:7" s="15" customFormat="1" ht="45" customHeight="1">
+      <c r="A5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>0.93</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>0.37</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="15">
         <v>4</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="45" customHeight="1">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1430,14 +2080,14 @@
       <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="45" customHeight="1">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1453,14 +2103,14 @@
       <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <v>3</v>
       </c>
       <c r="G7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="45" customHeight="1">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1476,15 +2126,15 @@
       <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <v>1</v>
       </c>
       <c r="G8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:7" ht="45" customHeight="1">
+      <c r="A9" s="12" t="s">
         <v>47</v>
       </c>
       <c r="B9" t="s">
@@ -1499,14 +2149,14 @@
       <c r="E9" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <v>4</v>
       </c>
       <c r="G9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="45" customHeight="1">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -1522,14 +2172,14 @@
       <c r="E10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <v>4</v>
       </c>
       <c r="G10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="45" customHeight="1">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -1545,7 +2195,7 @@
       <c r="E11" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="15">
         <v>3</v>
       </c>
       <c r="G11" t="s">
@@ -1560,15 +2210,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6884FD-D810-4C3C-B2DA-2BD5C476AC9B}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.5" customWidth="1"/>
-    <col min="2" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.95">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1591,7 +2241,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="45" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>65</v>
       </c>
@@ -1614,7 +2264,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="45" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>71</v>
       </c>
@@ -1628,50 +2278,50 @@
         <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="8">
-        <v>4</v>
+        <v>69</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" customHeight="1">
       <c r="A4" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="8">
         <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>69</v>
@@ -1680,44 +2330,44 @@
         <v>1</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="45" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>69</v>
@@ -1726,35 +2376,35 @@
         <v>2</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="8">
         <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="9">
         <v>0.25</v>
@@ -1766,59 +2416,59 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" s="8">
         <v>4</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F11" s="8">
         <v>3</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1828,270 +2478,267 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E4AEFC-0788-44F2-9EC2-DE1DF007568C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E34183-FA2C-4C47-BFEA-549D551F3EEF}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="45.5" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="11" t="s">
+    <row r="2" spans="1:7" ht="48">
+      <c r="A2" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="B2" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="C2" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F2">
+      <c r="D2" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="19">
         <v>3</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="G2" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="11" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="32.1">
+      <c r="A3" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="B3" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="C3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G3" s="11" t="s">
+      <c r="D3" s="19" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="E3" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="F3" s="19">
+        <v>3</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="11" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="32.1">
+      <c r="A4" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="B4" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="C4" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="F4">
+      <c r="D4" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="19">
+        <v>2</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32.1">
+      <c r="A5" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="19">
+        <v>4</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="48">
+      <c r="A6" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="19">
         <v>3</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5">
+      <c r="G6" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="63.95">
+      <c r="A7" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="19">
         <v>3</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" t="s">
-        <v>229</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7">
+      <c r="G7" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="63.95">
+      <c r="A8" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="19">
         <v>3</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" t="s">
-        <v>229</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="G8" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C9" s="11" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="48">
+      <c r="A9" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="B9" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="C9" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="s">
+      <c r="D9" s="19" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="E9" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="F9" s="19">
+        <v>3</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="11" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="32.1">
+      <c r="A10" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="B10" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="C10" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="F10">
+      <c r="D10" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="19">
         <v>2</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="48" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="G10" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="11" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="63.95">
+      <c r="A11" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="B11" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="C11" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="F11" t="s">
-        <v>228</v>
-      </c>
-      <c r="G11" s="11" t="s">
+      <c r="D11" s="19" t="s">
         <v>177</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="19">
+        <v>3</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2100,17 +2747,960 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156FF779-9700-410A-9F83-16A4B54347E3}">
-  <dimension ref="A1:W18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E4AEFC-0788-44F2-9EC2-DE1DF007568C}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.5" customWidth="1"/>
-    <col min="2" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="45.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="45" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="48">
+      <c r="A3" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="48">
+      <c r="A4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="48">
+      <c r="A5" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="48">
+      <c r="A6" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="48">
+      <c r="A7" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="48">
+      <c r="A8" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="48">
+      <c r="A9" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="32.1">
+      <c r="A10" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="48">
+      <c r="A11" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="48">
+      <c r="A12" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F66B882-905E-4B8F-8A8D-86191091445E}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" customWidth="1"/>
+    <col min="7" max="7" width="57.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="51" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="24">
+        <v>3</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="51" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="24">
+        <v>4</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="51" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="51" customHeight="1">
+      <c r="A5" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="51" customHeight="1">
+      <c r="A6" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="51" customHeight="1">
+      <c r="A7" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="20"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="12"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="20"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904F9C6D-D76F-4734-AA05-7BC252C29A9F}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="24">
+        <v>3</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="24">
+        <v>4</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A5" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A6" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A7" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60.75" customHeight="1">
+      <c r="A8" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="30">
+        <v>2</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="20"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="12"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="20"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="21"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326A30F8-149A-4CFF-823D-82326ADA27D6}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="63.95">
+      <c r="A2" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="F2" s="19">
+        <v>2</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="48">
+      <c r="A3" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="19">
+        <v>3</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="48">
+      <c r="A4" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" s="19">
+        <v>4</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="63.95">
+      <c r="A5" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="19">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="48">
+      <c r="A6" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F6" s="19">
+        <v>3</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="48">
+      <c r="A7" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="19">
+        <v>3</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="63.95">
+      <c r="A8" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F8" s="19">
+        <v>3</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="63.95">
+      <c r="A9" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="F9" s="19">
+        <v>3</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="48">
+      <c r="A10" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" s="19">
+        <v>3</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156FF779-9700-410A-9F83-16A4B54347E3}">
+  <dimension ref="A1:W18"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="15.95">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2149,27 +3739,27 @@
       <c r="V1" s="6"/>
       <c r="W1" s="6"/>
     </row>
-    <row r="2" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>339</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>179</v>
+        <v>340</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>180</v>
+        <v>341</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
+        <v>342</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>182</v>
+        <v>343</v>
       </c>
       <c r="F2" s="3">
         <v>2</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>183</v>
+        <v>344</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2188,27 +3778,27 @@
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
     </row>
-    <row r="3" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="45" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>345</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>346</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>347</v>
       </c>
       <c r="F3" s="3">
         <v>3</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>348</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2227,9 +3817,9 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
     </row>
-    <row r="4" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="45" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>188</v>
+        <v>349</v>
       </c>
       <c r="B4" s="7">
         <v>0.4</v>
@@ -2247,7 +3837,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2266,27 +3856,27 @@
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
     </row>
-    <row r="5" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="45" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>351</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>191</v>
+        <v>352</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
+        <v>353</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>193</v>
+        <v>354</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>194</v>
+        <v>355</v>
       </c>
       <c r="F5" s="3">
         <v>3</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>195</v>
+        <v>356</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -2305,27 +3895,27 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
     </row>
-    <row r="6" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="45" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>357</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>197</v>
+        <v>358</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>198</v>
+        <v>359</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>200</v>
+        <v>361</v>
       </c>
       <c r="F6" s="3">
         <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>201</v>
+        <v>362</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2344,27 +3934,27 @@
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
     </row>
-    <row r="7" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="45" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>203</v>
+        <v>364</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>365</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>205</v>
+        <v>366</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>206</v>
+        <v>367</v>
       </c>
       <c r="F7" s="3">
         <v>3</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>207</v>
+        <v>368</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2383,27 +3973,27 @@
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
     </row>
-    <row r="8" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="45" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>369</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>209</v>
+        <v>370</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>210</v>
+        <v>371</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>211</v>
+        <v>372</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>212</v>
+        <v>373</v>
       </c>
       <c r="F8" s="3">
         <v>3</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>213</v>
+        <v>374</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -2422,27 +4012,27 @@
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
     </row>
-    <row r="9" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="45" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>214</v>
+        <v>375</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>215</v>
+        <v>376</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>216</v>
+        <v>377</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>378</v>
       </c>
       <c r="F9" s="3">
         <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>218</v>
+        <v>379</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -2461,27 +4051,27 @@
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
     </row>
-    <row r="10" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="45" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>380</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>220</v>
+        <v>381</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>221</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>222</v>
+        <v>383</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>223</v>
+        <v>384</v>
       </c>
       <c r="F10" s="3">
         <v>3</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>224</v>
+        <v>385</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -2500,9 +4090,9 @@
       <c r="V10" s="6"/>
       <c r="W10" s="6"/>
     </row>
-    <row r="11" spans="1:23" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="30.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>225</v>
+        <v>386</v>
       </c>
       <c r="B11" s="7">
         <v>0.5</v>
@@ -2511,7 +4101,7 @@
         <v>0.65</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>226</v>
+        <v>387</v>
       </c>
       <c r="E11" s="7">
         <v>0.8</v>
@@ -2520,7 +4110,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
@@ -2539,7 +4129,7 @@
       <c r="V11" s="6"/>
       <c r="W11" s="6"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2564,7 +4154,7 @@
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -2589,7 +4179,7 @@
       <c r="V13" s="6"/>
       <c r="W13" s="6"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -2614,7 +4204,7 @@
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -2639,7 +4229,7 @@
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -2664,7 +4254,7 @@
       <c r="V16" s="6"/>
       <c r="W16" s="6"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2689,7 +4279,7 @@
       <c r="V17" s="6"/>
       <c r="W17" s="6"/>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2720,17 +4310,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2739,7 +4318,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -2980,40 +4559,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3297AE6B-7290-41A0-9746-30DE86CD2FB7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCA3780-F106-40B2-A3C7-BAC49BED8197}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCA3780-F106-40B2-A3C7-BAC49BED8197}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B905A20-ED86-463E-9E67-AFAF052897E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B905A20-ED86-463E-9E67-AFAF052897E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
-    <ds:schemaRef ds:uri="c8670835-afc4-4376-8ae0-1ffed5b27e6b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3297AE6B-7290-41A0-9746-30DE86CD2FB7}"/>
 </file>
--- a/02_Inputs/SEA Quizzes.xlsx
+++ b/02_Inputs/SEA Quizzes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29415"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/SEHCoreTeam/Shared Documents/General/04. Sustainable Energy Academy/SEA Quizzes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{070FAC4B-D145-4859-B9E3-DA8B24BBCF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="11_93AB3AFE6250B6AEC073F08D6A08556BFA9C6C66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{277F729E-AF24-4060-BBCB-CB397C25EDFC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21800" windowHeight="12980" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28960" windowHeight="16120" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Module 6" sheetId="9" r:id="rId7"/>
     <sheet name="Module 7" sheetId="7" r:id="rId8"/>
     <sheet name="Module 8" sheetId="2" r:id="rId9"/>
+    <sheet name="DREI (Module 9)" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,6 +48,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={E6EF8B3A-ED59-4224-88A2-5BC1F31D3847}</author>
+    <author>tc={3F3B525E-B771-45B9-AEFC-64847453EC17}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{E6EF8B3A-ED59-4224-88A2-5BC1F31D3847}">
@@ -57,12 +59,41 @@
     I</t>
       </text>
     </comment>
+    <comment ref="A5" authorId="1" shapeId="0" xr:uid="{3F3B525E-B771-45B9-AEFC-64847453EC17}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    To change
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={1CBABEA5-42A5-47EB-AF9F-32CF475A2DD0}</author>
+  </authors>
+  <commentList>
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{1CBABEA5-42A5-47EB-AF9F-32CF475A2DD0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    @Christoph Dallmann there is controversy here - some literature consider subsidies as derisking instruments, whereas DREI consider them as direct financial incentives. I'd rather follow the DREI logic here
+Reply:
+    I have changed the answer to avoid the confusion to something that is definitly not seen as a financial derisking instrument (public awareness campaign)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="553">
   <si>
     <t>Question Text</t>
   </si>
@@ -787,6 +818,213 @@
     <t>Supportive instruments include feed-in tariffs, carbon pricing, and energy performance contracts. Fuel subsidies generally discourage renewables.</t>
   </si>
   <si>
+    <t>What are the three key principles of effective energy governance discussed in the module?</t>
+  </si>
+  <si>
+    <t>Effectiveness, Efficiency, and Equity</t>
+  </si>
+  <si>
+    <t>Accountability, Inclusiveness, and Effectiveness</t>
+  </si>
+  <si>
+    <t>Affordability, Sustainability, and Resilience</t>
+  </si>
+  <si>
+    <t>Participation, Enforcement, and Integrity</t>
+  </si>
+  <si>
+    <t>Effectiveness, accountability, and inclusiveness ensure energy policies are sound, fair, and participatory.</t>
+  </si>
+  <si>
+    <t>Which of the following best defines energy governance?</t>
+  </si>
+  <si>
+    <t>The enforcement of environmental regulations by government institutions</t>
+  </si>
+  <si>
+    <t>The management of climate financing mechanisms through public policy</t>
+  </si>
+  <si>
+    <t>The exercise of authority to manage the planning, production, and access to energy</t>
+  </si>
+  <si>
+    <t>The use of technology to reduce carbon emissions in energy systems</t>
+  </si>
+  <si>
+    <t>Energy governance involves political, economic, and social authority over energy decisions.</t>
+  </si>
+  <si>
+    <t>Why is energy governance critical in achieving a just energy transition?</t>
+  </si>
+  <si>
+    <t>It ensures new technologies are patented fairly</t>
+  </si>
+  <si>
+    <t>It controls global emissions through a single regulatory agency</t>
+  </si>
+  <si>
+    <t>It shapes how decisions are made, trade-offs are managed, and policies are implemented</t>
+  </si>
+  <si>
+    <t>It focuses solely on reducing fossil fuel subsidies</t>
+  </si>
+  <si>
+    <t>Governance shapes policies and implementation, crucial for managing transition trade-offs.</t>
+  </si>
+  <si>
+    <t>What does “fossil fuel lock-in” refer to?</t>
+  </si>
+  <si>
+    <t>Fossil fuels becoming inaccessible due to international sanctions</t>
+  </si>
+  <si>
+    <t>Political and economic dependence on fossil fuels, making transition difficult</t>
+  </si>
+  <si>
+    <t>Locking fossil fuels in underground reserves through carbon capture</t>
+  </si>
+  <si>
+    <t>Binding international contracts that prevent the use of renewables</t>
+  </si>
+  <si>
+    <t>Fossil fuel lock-in ties economies and institutions to fossil fuel dependence.</t>
+  </si>
+  <si>
+    <t>Which governance approach emphasizes collaboration across multiple levels and sectors?</t>
+  </si>
+  <si>
+    <t>Top-down governance</t>
+  </si>
+  <si>
+    <t>Adaptive enforcement</t>
+  </si>
+  <si>
+    <t>Multi-level governance</t>
+  </si>
+  <si>
+    <t>Financial centralization</t>
+  </si>
+  <si>
+    <t>Multi-level governance coordinates actions across levels and sectors.</t>
+  </si>
+  <si>
+    <t>What tool is used to analyze how power and institutions shape policy outcomes in energy governance?</t>
+  </si>
+  <si>
+    <t>Green Climate Fund (GCF)</t>
+  </si>
+  <si>
+    <t>Institutional and Context Analysis (ICA)</t>
+  </si>
+  <si>
+    <t>Renewable Investment Index (RII)</t>
+  </si>
+  <si>
+    <t>Emissions Trading Scheme (ETS)</t>
+  </si>
+  <si>
+    <t>ICA identifies power dynamics and institutional barriers in policy processes.</t>
+  </si>
+  <si>
+    <t>According to the Paris Agreement, how are energy transitions now treated compared to earlier frameworks like the UNFCCC?</t>
+  </si>
+  <si>
+    <t>As side effects of agricultural transformation</t>
+  </si>
+  <si>
+    <t>As central policy levers essential for meeting climate goals</t>
+  </si>
+  <si>
+    <t>As voluntary measures with no legal standing</t>
+  </si>
+  <si>
+    <t>As actions to be undertaken solely by developed countries</t>
+  </si>
+  <si>
+    <t>The Paris Agreement centralizes energy transitions to meet climate goals.</t>
+  </si>
+  <si>
+    <t>What percentage of Nationally Determined Contributions (NDCs) explicitly address just transition according to the synthesis report?</t>
+  </si>
+  <si>
+    <t>Only 31% of NDCs address just transition impacts on vulnerable groups.</t>
+  </si>
+  <si>
+    <t>Which foresight method starts by defining a desired future and then maps steps backward?</t>
+  </si>
+  <si>
+    <t>Scenario Planning</t>
+  </si>
+  <si>
+    <t>Visioning</t>
+  </si>
+  <si>
+    <t>Backcasting</t>
+  </si>
+  <si>
+    <t>Horizon Mapping</t>
+  </si>
+  <si>
+    <t>Backcasting is a foresight technique that begins with a desirable future and maps necessary steps to reach that vision.</t>
+  </si>
+  <si>
+    <t>What is the primary goal of a Whole-of-Government approach in energy governance?</t>
+  </si>
+  <si>
+    <t>To centralize power under the Ministry of Energy</t>
+  </si>
+  <si>
+    <t>To foster inter-ministerial collaboration and policy coherence</t>
+  </si>
+  <si>
+    <t>To reduce the role of parliament in energy governance</t>
+  </si>
+  <si>
+    <t>To manage regional transmission infrastructure</t>
+  </si>
+  <si>
+    <t>Whole-of-Government approaches integrate cross-ministerial collaboration to promote cohesive energy policy aligned with broader development goals.</t>
+  </si>
+  <si>
+    <t>Which of the following best defines agile oversight in the energy sector?</t>
+  </si>
+  <si>
+    <t>A fixed, rule-based enforcement mechanism</t>
+  </si>
+  <si>
+    <t>A responsive, real-time monitoring mechanism</t>
+  </si>
+  <si>
+    <t>A gender-based budgeting system</t>
+  </si>
+  <si>
+    <t>A tool for subsidy disbursement</t>
+  </si>
+  <si>
+    <t>Agile oversight refers to real-time, adaptive monitoring that supports flexible decision-making and policy responsiveness in evolving contexts.</t>
+  </si>
+  <si>
+    <t>Which of the following mechanisms are critical to external oversight in energy governance?</t>
+  </si>
+  <si>
+    <t>Regulatory enforcement of service standards</t>
+  </si>
+  <si>
+    <t>Community-based grievance redress systems</t>
+  </si>
+  <si>
+    <t>Parliamentary review committees</t>
+  </si>
+  <si>
+    <t>Centralized tariff-setting authorities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2, 3 </t>
+  </si>
+  <si>
+    <t>External oversight includes formal regulatory and legislative mechanisms as well as participatory approaches, all aimed at ensuring transparency and accountability.</t>
+  </si>
+  <si>
     <t>What percentage of total global greenhouse gas emissions is attributed to the energy sector?</t>
   </si>
   <si>
@@ -820,7 +1058,7 @@
     <t>Sulfur hexafluoride (SF₆)</t>
   </si>
   <si>
-    <t>SF₆ has the highest GWP—about 25,200 times that of CO₂—making it a critical target for emission reductions in energy distribution.</t>
+    <t>SF₆ has the highest GWP about 25,200 times that of CO₂ making it a critical target for emission reductions in energy distribution.</t>
   </si>
   <si>
     <t>What are key environmental impacts associated with the development of renewable energy infrastructure?</t>
@@ -919,6 +1157,27 @@
     <t>Transport is the largest source of end-use CO2 emissions, responsible for over one-third, making it a priority sector for decarbonization through electrification and efficiency improvements.</t>
   </si>
   <si>
+    <t>Why is lifecycle emissions analysis critical for comparing renewable and fossil energy technologies?</t>
+  </si>
+  <si>
+    <t>Because it reveals true emissions impacts beyond the point of use</t>
+  </si>
+  <si>
+    <t>Because it measures only the emissions from fuel combustion</t>
+  </si>
+  <si>
+    <t>Because renewables can show lower total emissions even after including manufacturing and disposal</t>
+  </si>
+  <si>
+    <t>Because it’s the only metric governments use to set climate targets</t>
+  </si>
+  <si>
+    <t>1, 3</t>
+  </si>
+  <si>
+    <t>Lifecycle analysis includes emissions from construction, use, and decommissioning. It highlights how renewables remain lower-emission even when all stages are considered.</t>
+  </si>
+  <si>
     <t>A Ministry of Energy seeks to optimize off-grid investments in underserved rural zones but has limited household-level data. Which of the following techniques could most effectively identify priority areas for electrification?</t>
   </si>
   <si>
@@ -938,15 +1197,20 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Which of the following is a </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>necessary condition</t>
@@ -954,9 +1218,8 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> for using energy data to support gender-transformative policy design?</t>
@@ -1299,12 +1562,276 @@
   <si>
     <t>According to IPCC-aligned pathways, nearly all new capacity additions by 2050 are expected to be from renewables.</t>
   </si>
+  <si>
+    <t>1. Which SDGs are most directly linked to renewable energy investment in developing countries?</t>
+  </si>
+  <si>
+    <t>SDG 7 &amp; SDG 13</t>
+  </si>
+  <si>
+    <t>SDG 1 &amp; SDG 7</t>
+  </si>
+  <si>
+    <t>SDG 3 &amp; SDG 5</t>
+  </si>
+  <si>
+    <t>SDG 9 &amp; SDG 12</t>
+  </si>
+  <si>
+    <t>Renewable energy advances SDG 7 (energy access), SDG 13 (climate action), and SDG 1 (poverty reduction).</t>
+  </si>
+  <si>
+    <t>2. What is the main barrier for renewable energy competitiveness in developing countries?</t>
+  </si>
+  <si>
+    <t>High technology costs</t>
+  </si>
+  <si>
+    <t>Lack of sunlight</t>
+  </si>
+  <si>
+    <t>Fuel shortages</t>
+  </si>
+  <si>
+    <t>Renewables are capital-intensive; high financing costs reduce competitiveness.</t>
+  </si>
+  <si>
+    <t>3. Which of the following are decentralized renewable energy systems?</t>
+  </si>
+  <si>
+    <t>Utility-scale solar</t>
+  </si>
+  <si>
+    <t>Solar mini-grids</t>
+  </si>
+  <si>
+    <t>Rooftop PV</t>
+  </si>
+  <si>
+    <t>Solar Home Systems</t>
+  </si>
+  <si>
+    <t>2, 3, 4</t>
+  </si>
+  <si>
+    <t>Mini-grids, rooftops, and SHS are decentralized; utility-scale plants are centralized.</t>
+  </si>
+  <si>
+    <t>4. What does LCOE stand for?</t>
+  </si>
+  <si>
+    <t>Levelized Cost of Energy</t>
+  </si>
+  <si>
+    <t>Localized Cost of Equity</t>
+  </si>
+  <si>
+    <t>Long-term Cost of Electricity</t>
+  </si>
+  <si>
+    <t>Low-carbon Operational Expense</t>
+  </si>
+  <si>
+    <t>LCOE measures average lifetime electricity cost, crucial for comparing technologies.</t>
+  </si>
+  <si>
+    <t>5. In project finance, what is the role of a Special Purpose Vehicle (SPV)?</t>
+  </si>
+  <si>
+    <t>Provides subsidies</t>
+  </si>
+  <si>
+    <t>Holds project contracts &amp; raises capital</t>
+  </si>
+  <si>
+    <t>Buys electricity</t>
+  </si>
+  <si>
+    <t>Sets tariffs</t>
+  </si>
+  <si>
+    <t>The SPV isolates project risks and serves as the legal entity for financing.</t>
+  </si>
+  <si>
+    <t>6. Which type of capital absorbs the first losses in a project?</t>
+  </si>
+  <si>
+    <t>Debt</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Subsidies</t>
+  </si>
+  <si>
+    <t>Concessional support</t>
+  </si>
+  <si>
+    <t>Equity investors bear first losses but expect higher returns.</t>
+  </si>
+  <si>
+    <t>7. What are the first three stages of the DREI methodology?</t>
+  </si>
+  <si>
+    <t>Risk Environment, Public Instruments, LCOE</t>
+  </si>
+  <si>
+    <t>Risk Environment, LCOE, Evaluation</t>
+  </si>
+  <si>
+    <t>Public Instruments, Evaluation, Policy</t>
+  </si>
+  <si>
+    <t>LCOE, Subsidies, Financing</t>
+  </si>
+  <si>
+    <t>The first three stages are Risk Environment, Public Instruments, and LCOE.</t>
+  </si>
+  <si>
+    <t>8. What is the main purpose of public derisking instruments?</t>
+  </si>
+  <si>
+    <t>Increase electricity demand</t>
+  </si>
+  <si>
+    <t>Reduce investment risks</t>
+  </si>
+  <si>
+    <t>Provide free electricity</t>
+  </si>
+  <si>
+    <t>Increase fossil fuel competitiveness</t>
+  </si>
+  <si>
+    <t>Public instruments improve the risk-return profile to attract private capital.</t>
+  </si>
+  <si>
+    <t>9. Which of the following are examples of policy derisking instruments?</t>
+  </si>
+  <si>
+    <t>Concessional loans</t>
+  </si>
+  <si>
+    <t>Regulatory reform</t>
+  </si>
+  <si>
+    <t>Capacity building</t>
+  </si>
+  <si>
+    <t>3, 4</t>
+  </si>
+  <si>
+    <t>Policy derisking reduces risks via regulation, standards, and capacity measures.</t>
+  </si>
+  <si>
+    <t>10. Which of the following are financial derisking instruments?</t>
+  </si>
+  <si>
+    <t>Public awareness campaigns</t>
+  </si>
+  <si>
+    <t>Training programs</t>
+  </si>
+  <si>
+    <t>Financial derisking includes tools like guarantees and concessional loans. Awareness campaigns and training don’t directly reduce financing risks.</t>
+  </si>
+  <si>
+    <t>11. What is the purpose of the Financing Costs Waterfall in DREI?</t>
+  </si>
+  <si>
+    <t>Show technology costs</t>
+  </si>
+  <si>
+    <t>Visualize impact of risks on financing terms</t>
+  </si>
+  <si>
+    <t>Compare fossil vs. renewable plants</t>
+  </si>
+  <si>
+    <t>Estimate carbon emissions</t>
+  </si>
+  <si>
+    <t>The waterfall shows how risks affect cost of equity and debt.</t>
+  </si>
+  <si>
+    <t>12. What is a viability gap in renewable energy projects?</t>
+  </si>
+  <si>
+    <t>Difference between demand and supply</t>
+  </si>
+  <si>
+    <t>Gap between project cost and investor returns</t>
+  </si>
+  <si>
+    <t>Shortage of skilled staff</t>
+  </si>
+  <si>
+    <t>Time lag in policy implementation</t>
+  </si>
+  <si>
+    <t>The viability gap is the shortfall between affordable costs and investor requirements.</t>
+  </si>
+  <si>
+    <t>13. What does the “cost of capital” mean in renewable energy projects?</t>
+  </si>
+  <si>
+    <t>The price of e.g. solar panels</t>
+  </si>
+  <si>
+    <t>The return that lenders and investors expect</t>
+  </si>
+  <si>
+    <t>The yearly cost of maintenance</t>
+  </si>
+  <si>
+    <t>Money given by the government</t>
+  </si>
+  <si>
+    <t>Cost of capital is the money that investors and banks want to earn back when they fund a project.</t>
+  </si>
+  <si>
+    <t>14. Why do we calculate Net Present Value (NPV) for a project?</t>
+  </si>
+  <si>
+    <t>To measure pollution</t>
+  </si>
+  <si>
+    <t>To check how much equipment costs</t>
+  </si>
+  <si>
+    <t>To see if the project will make money over time</t>
+  </si>
+  <si>
+    <t>To count government subsidies</t>
+  </si>
+  <si>
+    <t>NPV tells us if a project will bring in more money than it costs, after considering future cash flows.</t>
+  </si>
+  <si>
+    <t>15. What is the ultimate objective of the DREI framework?</t>
+  </si>
+  <si>
+    <t>Maximize government subsidies</t>
+  </si>
+  <si>
+    <t>Reduce fossil fuel dependence only</t>
+  </si>
+  <si>
+    <t>Attract private investment cost-effectively</t>
+  </si>
+  <si>
+    <t>Build renewable plants directly</t>
+  </si>
+  <si>
+    <t>DREI helps policymakers reduce risks and costs to mobilize private capital.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1376,21 +1903,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -1410,13 +1922,60 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1426,6 +1985,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1440,16 +2005,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1457,7 +2022,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1498,29 +2063,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1540,6 +2129,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Christoph Dallmann" id="{80D227A4-EF08-EA40-AD0C-4461019CA1BC}" userId="christoph.dallmann@undp.org" providerId="PeoplePicker"/>
+  <person displayName="Laurene Desclaux" id="{6284D123-B7D8-A546-B1F4-21D17366A403}" userId="S::laurene.desclaux@undp.org::4fa17dca-caa4-41bf-a230-0ec0bff17f33" providerId="AD"/>
+  <person displayName="Christoph Dallmann" id="{555FBE29-16F4-E24A-8179-41C26F8ADD49}" userId="S::christoph.dallmann@undp.org::8f3de4e5-ded4-4dc0-a932-000062049854" providerId="AD"/>
   <person displayName="Folashade Jaiyeola" id="{468EB6D1-28C8-4738-B29C-83F7AD58AB30}" userId="S::folashade.jaiyeola@undp.org::c208a32e-6303-48b2-9538-645490e99643" providerId="AD"/>
 </personList>
 </file>
@@ -1864,6 +2456,24 @@
   <threadedComment ref="A2" dT="2025-06-06T19:29:09.26" personId="{468EB6D1-28C8-4738-B29C-83F7AD58AB30}" id="{E6EF8B3A-ED59-4224-88A2-5BC1F31D3847}">
     <text>I</text>
   </threadedComment>
+  <threadedComment ref="A5" dT="2025-06-24T14:33:52.88" personId="{468EB6D1-28C8-4738-B29C-83F7AD58AB30}" id="{3F3B525E-B771-45B9-AEFC-64847453EC17}">
+    <text xml:space="preserve">To change
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G11" dT="2025-09-23T14:49:03.35" personId="{6284D123-B7D8-A546-B1F4-21D17366A403}" id="{1CBABEA5-42A5-47EB-AF9F-32CF475A2DD0}">
+    <text>@Christoph Dallmann there is controversy here - some literature consider subsidies as derisking instruments, whereas DREI consider them as direct financial incentives. I'd rather follow the DREI logic here</text>
+    <mentions>
+      <mention mentionpersonId="{80D227A4-EF08-EA40-AD0C-4461019CA1BC}" mentionId="{99E2F96A-C739-4290-930F-857DAAC84188}" startIndex="0" length="19"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="G11" dT="2025-09-23T16:06:10.22" personId="{555FBE29-16F4-E24A-8179-41C26F8ADD49}" id="{EC9ADD41-1C9D-5643-B686-7A9D660EA158}" parentId="{1CBABEA5-42A5-47EB-AF9F-32CF475A2DD0}">
+    <text>I have changed the answer to avoid the confusion to something that is definitly not seen as a financial derisking instrument (public awareness campaign)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1935,6 +2545,391 @@
     <row r="11" spans="1:7" ht="45" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33F3B1D-B984-4FAD-ABB9-EE6CB5DBECF5}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.42578125" customWidth="1"/>
+    <col min="2" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.95">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>469</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>472</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="F3" s="35">
+        <v>2</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" s="35">
+        <v>1</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>493</v>
+      </c>
+      <c r="F6" s="35">
+        <v>2</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="35" t="s">
+        <v>495</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>496</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>497</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>498</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>499</v>
+      </c>
+      <c r="F7" s="35">
+        <v>2</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="35" t="s">
+        <v>501</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>504</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="F8" s="35">
+        <v>1</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="35" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>509</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>511</v>
+      </c>
+      <c r="F9" s="35">
+        <v>2</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>521</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>524</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>525</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>527</v>
+      </c>
+      <c r="F12" s="35">
+        <v>2</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="35" t="s">
+        <v>529</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>530</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>531</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>532</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>533</v>
+      </c>
+      <c r="F13" s="35">
+        <v>2</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>536</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>537</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>538</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>539</v>
+      </c>
+      <c r="F14" s="35">
+        <v>2</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="35" t="s">
+        <v>541</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>542</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>543</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>544</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>545</v>
+      </c>
+      <c r="F15" s="35">
+        <v>3</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="35" t="s">
+        <v>547</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>548</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>549</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>550</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>551</v>
+      </c>
+      <c r="F16" s="35">
+        <v>3</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2311,7 +3306,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="34" t="s">
         <v>83</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -2380,7 +3375,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="34" t="s">
         <v>99</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -3043,189 +4038,317 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F66B882-905E-4B8F-8A8D-86191091445E}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
-    <col min="5" max="5" width="33.7109375" customWidth="1"/>
-    <col min="7" max="7" width="57.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="12"/>
+    <col min="7" max="7" width="57.42578125" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.95">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:7" s="24" customFormat="1" ht="51" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="51" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="20">
+        <v>2</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="51" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="20">
         <v>3</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="51" customHeight="1">
-      <c r="A3" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F3" s="24">
+      <c r="G3" s="20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="51" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="20">
+        <v>3</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="51" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="20">
+        <v>2</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="51" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="F6" s="20">
+        <v>3</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="42.95">
+      <c r="A7" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" s="20">
+        <v>2</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="57">
+      <c r="A8" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="20">
+        <v>2</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="57">
+      <c r="A9" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="21">
+        <v>0.17</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="21">
+        <v>0.31</v>
+      </c>
+      <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="51" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="51" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="51" customHeight="1">
-      <c r="A6" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="51" customHeight="1">
-      <c r="A7" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="20"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="12"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
+      <c r="G9" s="20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="42.95">
+      <c r="A10" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="F10" s="20">
+        <v>3</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="42.95">
+      <c r="A11" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F11" s="20">
+        <v>2</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.1">
+      <c r="A12" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F12" s="20">
+        <v>2</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48">
+      <c r="A13" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>309</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3235,207 +4358,229 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904F9C6D-D76F-4734-AA05-7BC252C29A9F}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.1"/>
   <cols>
-    <col min="1" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="36.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="30"/>
+    <col min="7" max="7" width="36.42578125" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.95">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:7" s="29" customFormat="1" ht="17.100000000000001">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A2" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="F2" s="24">
+      <c r="A2" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="F2" s="26">
         <v>3</v>
       </c>
-      <c r="G2" s="23" t="s">
-        <v>246</v>
+      <c r="G2" s="26" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A3" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F3" s="24">
+      <c r="A3" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="26">
         <v>4</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>252</v>
+      <c r="G3" s="26" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>259</v>
+      <c r="A4" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>266</v>
+      <c r="A5" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A6" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>272</v>
+      <c r="A6" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A7" s="23" t="s">
-        <v>273</v>
+      <c r="A7" s="26" t="s">
+        <v>342</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="60.75" customHeight="1">
-      <c r="A8" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="F8" s="30">
+      <c r="A8" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="31">
         <v>2</v>
       </c>
-      <c r="G8" s="30" t="s">
-        <v>284</v>
+      <c r="G8" s="31" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="75">
+      <c r="A9" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>356</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="20"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="12"/>
+      <c r="A11" s="29"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="20"/>
+      <c r="A13" s="29"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="21"/>
+      <c r="A14" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3478,209 +4623,209 @@
     </row>
     <row r="2" spans="1:7" ht="63.95">
       <c r="A2" s="19" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>288</v>
+        <v>364</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="F2" s="19">
         <v>2</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="48">
-      <c r="A3" s="19" t="s">
-        <v>291</v>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.5">
+      <c r="A3" s="36" t="s">
+        <v>367</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="F3" s="19">
         <v>3</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>296</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="48">
       <c r="A4" s="19" t="s">
-        <v>297</v>
+        <v>373</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>298</v>
+        <v>374</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="F4" s="19">
         <v>4</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>302</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="63.95">
       <c r="A5" s="19" t="s">
-        <v>303</v>
+        <v>379</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>305</v>
+        <v>381</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>306</v>
+        <v>382</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>307</v>
+        <v>383</v>
       </c>
       <c r="F5" s="19">
         <v>1</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>308</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="48">
       <c r="A6" s="19" t="s">
-        <v>309</v>
+        <v>385</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>311</v>
+        <v>387</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>312</v>
+        <v>388</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
       <c r="F6" s="19">
         <v>3</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>314</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="48">
       <c r="A7" s="19" t="s">
-        <v>315</v>
+        <v>391</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>316</v>
+        <v>392</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>317</v>
+        <v>393</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>318</v>
+        <v>394</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>319</v>
+        <v>395</v>
       </c>
       <c r="F7" s="19">
         <v>3</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>320</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="63.95">
       <c r="A8" s="19" t="s">
-        <v>321</v>
+        <v>397</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>323</v>
+        <v>399</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>324</v>
+        <v>400</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="F8" s="19">
         <v>3</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="63.95">
       <c r="A9" s="19" t="s">
-        <v>327</v>
+        <v>403</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>328</v>
+        <v>404</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>329</v>
+        <v>405</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>330</v>
+        <v>406</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>331</v>
+        <v>407</v>
       </c>
       <c r="F9" s="19">
         <v>3</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>332</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="48">
       <c r="A10" s="19" t="s">
-        <v>333</v>
+        <v>409</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>334</v>
+        <v>410</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>335</v>
+        <v>411</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>336</v>
+        <v>412</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>337</v>
+        <v>413</v>
       </c>
       <c r="F10" s="19">
         <v>3</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>338</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1"/>
@@ -3741,25 +4886,25 @@
     </row>
     <row r="2" spans="1:23" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>339</v>
+        <v>415</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>340</v>
+        <v>416</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>341</v>
+        <v>417</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>342</v>
+        <v>418</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>343</v>
+        <v>419</v>
       </c>
       <c r="F2" s="3">
         <v>2</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -3780,25 +4925,25 @@
     </row>
     <row r="3" spans="1:23" ht="45" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>345</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="F3" s="3">
         <v>3</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>348</v>
+        <v>424</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -3819,7 +4964,7 @@
     </row>
     <row r="4" spans="1:23" ht="45" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>349</v>
+        <v>425</v>
       </c>
       <c r="B4" s="7">
         <v>0.4</v>
@@ -3837,7 +4982,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>350</v>
+        <v>426</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -3858,25 +5003,25 @@
     </row>
     <row r="5" spans="1:23" ht="45" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>351</v>
+        <v>427</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>352</v>
+        <v>428</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>353</v>
+        <v>429</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>354</v>
+        <v>430</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="F5" s="3">
         <v>3</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -3897,25 +5042,25 @@
     </row>
     <row r="6" spans="1:23" ht="45" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>357</v>
+        <v>433</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>359</v>
+        <v>435</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>361</v>
+        <v>437</v>
       </c>
       <c r="F6" s="3">
         <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>362</v>
+        <v>438</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -3936,25 +5081,25 @@
     </row>
     <row r="7" spans="1:23" ht="45" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>363</v>
+        <v>439</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>364</v>
+        <v>440</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>365</v>
+        <v>441</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>366</v>
+        <v>442</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>367</v>
+        <v>443</v>
       </c>
       <c r="F7" s="3">
         <v>3</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>368</v>
+        <v>444</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -3975,25 +5120,25 @@
     </row>
     <row r="8" spans="1:23" ht="45" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>369</v>
+        <v>445</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>371</v>
+        <v>447</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>372</v>
+        <v>448</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>373</v>
+        <v>449</v>
       </c>
       <c r="F8" s="3">
         <v>3</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>374</v>
+        <v>450</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -4014,25 +5159,25 @@
     </row>
     <row r="9" spans="1:23" ht="45" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>375</v>
+        <v>451</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>376</v>
+        <v>452</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>377</v>
+        <v>453</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>221</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>378</v>
+        <v>454</v>
       </c>
       <c r="F9" s="3">
         <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>379</v>
+        <v>455</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
@@ -4053,25 +5198,25 @@
     </row>
     <row r="10" spans="1:23" ht="45" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>380</v>
+        <v>456</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>381</v>
+        <v>457</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>383</v>
+        <v>459</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>384</v>
+        <v>460</v>
       </c>
       <c r="F10" s="3">
         <v>3</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -4092,7 +5237,7 @@
     </row>
     <row r="11" spans="1:23" ht="30.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
       <c r="B11" s="7">
         <v>0.5</v>
@@ -4101,7 +5246,7 @@
         <v>0.65</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>387</v>
+        <v>463</v>
       </c>
       <c r="E11" s="7">
         <v>0.8</v>
@@ -4110,7 +5255,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>388</v>
+        <v>464</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
@@ -4310,6 +5455,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4318,7 +5474,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098970033F315F542A2D9640B7CC02236" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94449e8ff35cec47b43afd2e381d9e90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3" xmlns:ns3="c8670835-afc4-4376-8ae0-1ffed5b27e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f21ad7dc1dad656b5a5a7699096a32" ns2:_="" ns3:_="">
     <xsd:import namespace="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3"/>
@@ -4559,25 +5715,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c8670835-afc4-4376-8ae0-1ffed5b27e6b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b0bf4113-6f4a-4f3e-b5bb-503c4d9102e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3297AE6B-7290-41A0-9746-30DE86CD2FB7}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCA3780-F106-40B2-A3C7-BAC49BED8197}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B905A20-ED86-463E-9E67-AFAF052897E1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3297AE6B-7290-41A0-9746-30DE86CD2FB7}"/>
 </file>